--- a/decks/katara_water_tribe.xlsx
+++ b/decks/katara_water_tribe.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.86" customWidth="1" min="1" max="1"/>
@@ -535,20 +535,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Airbender's Reversal</t>
+          <t>Ajani, Adversary of Tyrants</t>
         </is>
       </c>
       <c r="C2" t="b">
         <v>1</v>
       </c>
       <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Too narrow — only hits attacking creatures; replaced by Propaganda for persistent attack deterrence across all opponents.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>On Theme</t>
@@ -556,31 +552,31 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Mythic</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>TLA</t>
+          <t>J25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Airbender%27s%20Reversal&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Ajani%2C%20Adversary%20of%20Tyrants&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>$0.24</t>
+          <t>$0.94</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Choose one — • Destroy target attacking creature. • Airbend target creature you control. (Exile it. While it's exiled, its owner may cast it for {2} rather than its mana cost.)</t>
+          <t>+1: Put a +1/+1 counter on each of up to two target creatures. −2: Return target creature card with mana value 2 or less from your graveyard to the battlefield. −7: You get an emblem with "At the beginning of your end step, create three 1/1 white Cat creature tokens with lifelink."</t>
         </is>
       </c>
     </row>
@@ -628,7 +624,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>$5.51</t>
+          <t>$7.88</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -667,7 +663,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SOC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -681,7 +677,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>$0.51</t>
+          <t>$0.44</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -734,7 +730,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>$1.31</t>
+          <t>$1.11</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +783,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>$0.31</t>
+          <t>$0.29</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -840,7 +836,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>$0.36</t>
+          <t>$0.27</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +889,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>$0.18</t>
+          <t>$0.26</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -910,7 +906,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bident of Thassa</t>
+          <t>Bender's Waterskin</t>
         </is>
       </c>
       <c r="C9" t="b">
@@ -922,36 +918,36 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Card Advantage</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BLC</t>
+          <t>TLA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Bident%20of%20Thassa&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Bender%27s%20Waterskin&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>$0.37</t>
+          <t>$0.69</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Whenever a creature you control deals combat damage to a player, you may draw a card. {1}{U}, {T}: Creatures your opponents control attack this turn if able.</t>
+          <t>Untap this artifact during each other player's untap step. {T}: Add one mana of any color.</t>
         </is>
       </c>
     </row>
@@ -963,7 +959,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bygone Bishop</t>
+          <t>Boreas Charger</t>
         </is>
       </c>
       <c r="C10" t="b">
@@ -975,7 +971,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Card Advantage</t>
+          <t>On Theme</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -985,7 +981,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CLB</t>
+          <t>VOC</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -994,17 +990,17 @@
         </is>
       </c>
       <c r="J10">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Bygone%20Bishop&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Boreas%20Charger&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>$0.31</t>
+          <t>$0.32</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Flying Whenever you cast a creature spell with mana value 3 or less, investigate. (Create a Clue token. It's an artifact with "{2}, Sacrifice this token: Draw a card.")</t>
+          <t>Flying When this creature leaves the battlefield, choose an opponent who controls more lands than you. Search your library for a number of Plains cards equal to the difference, reveal those cards, put one of them onto the battlefield tapped and the rest into your hand, then shuffle.</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1012,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Captain of the Watch</t>
+          <t>Cathars' Crusade</t>
         </is>
       </c>
       <c r="C11" t="b">
@@ -1038,26 +1034,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PIP</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Captain%20of%20the%20Watch&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Cathars%27%20Crusade&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>$0.31</t>
+          <t>$9.37</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Vigilance (Attacking doesn't cause this creature to tap.) Other Soldier creatures you control get +1/+1 and have vigilance. When this creature enters, create three 1/1 white Soldier creature tokens.</t>
+          <t>Whenever a creature you control enters, put a +1/+1 counter on each creature you control.</t>
         </is>
       </c>
     </row>
@@ -1069,11 +1065,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cathars' Crusade</t>
+          <t>Chasm Skulker</t>
         </is>
       </c>
       <c r="C12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
@@ -1091,26 +1087,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>FIC</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Cathars%27%20Crusade&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Chasm%20Skulker&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>$8.07</t>
+          <t>$0.30</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Whenever a creature you control enters, put a +1/+1 counter on each creature you control.</t>
+          <t>Whenever you draw a card, put a +1/+1 counter on this creature. When this creature dies, create X 1/1 blue Squid creature tokens with islandwalk, where X is the number of +1/+1 counters on this creature. (They can't be blocked as long as defending player controls an Island.)</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1118,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clarion Spirit</t>
+          <t>Counterspell</t>
         </is>
       </c>
       <c r="C13" t="b">
@@ -1134,7 +1130,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1144,7 +1140,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PLST</t>
+          <t>DSC</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1153,17 +1149,17 @@
         </is>
       </c>
       <c r="J13">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Clarion%20Spirit&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Counterspell&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>$0.20</t>
+          <t>$3.56</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Whenever you cast your second spell each turn, create a 1/1 white Spirit creature token with flying.</t>
+          <t>Counter target spell.</t>
         </is>
       </c>
     </row>
@@ -1175,20 +1171,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Coastal Piracy</t>
+          <t>Darien, King of Kjeldor</t>
         </is>
       </c>
       <c r="C14" t="b">
         <v>1</v>
       </c>
       <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Weakest of the three attack-draw enchantments; replaced by Military Intelligence which draws whenever 2+ creatures attack — fires every combat in this wide token deck.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>On Theme</t>
@@ -1196,31 +1188,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Coastal%20Piracy&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Darien%2C%20King%20of%20Kjeldor&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$2.18</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Whenever a creature you control deals combat damage to an opponent, you may draw a card.</t>
+          <t>Whenever you're dealt damage, you may create that many 1/1 white Soldier creature tokens.</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1224,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Command Tower</t>
+          <t>Decree of Justice</t>
         </is>
       </c>
       <c r="C15" t="b">
@@ -1244,36 +1236,36 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lands</t>
+          <t>On Theme</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SOC</t>
+          <t>MH3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Command%20Tower&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Decree%20of%20Justice&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>$0.32</t>
+          <t>$0.19</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>{T}: Add one mana of any color in your commander's color identity.</t>
+          <t>Create X 4/4 white Angel creature tokens with flying. Cycling {2}{W} ({2}{W}, Discard this card: Draw a card.) When you cycle this card, you may pay {X}. If you do, create X 1/1 white Soldier creature tokens.</t>
         </is>
       </c>
     </row>
@@ -1285,11 +1277,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Counterspell</t>
+          <t>Divine Visitation</t>
         </is>
       </c>
       <c r="C16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
@@ -1297,36 +1289,36 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>On Theme</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Mythic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DSC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Counterspell&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Divine%20Visitation&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>$3.72</t>
+          <t>$0.46</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Counter target spell.</t>
+          <t>If one or more creature tokens would be created under your control, that many 4/4 white Angel creature tokens with flying and vigilance are created instead.</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1330,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Curious Farm Animals</t>
+          <t>Dovescape</t>
         </is>
       </c>
       <c r="C17" t="b">
@@ -1355,31 +1347,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TLA</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Curious%20Farm%20Animals&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Dovescape&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>$0.19</t>
+          <t>$4.40</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>When this creature dies, you gain 3 life. {2}, Sacrifice this creature: Destroy up to one target artifact or enchantment.</t>
+          <t>({W/U} can be paid with either {W} or {U}.) Whenever a player casts a noncreature spell, counter that spell. That player creates X 1/1 white and blue Bird creature tokens with flying, where X is the spell's mana value.</t>
         </is>
       </c>
     </row>
@@ -1391,20 +1383,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Decree of Justice</t>
+          <t>Entreat the Angels</t>
         </is>
       </c>
       <c r="C18" t="b">
         <v>1</v>
       </c>
       <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Both modes now covered — Entreat the Angels handles angels, Secure the Wastes handles instant-speed X tokens; replaced by Talrand, Sky Summoner for flying Drake generation on every instant or sorcery.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>On Theme</t>
@@ -1412,31 +1400,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Mythic</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MH3</t>
+          <t>DSC</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Decree%20of%20Justice&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Entreat%20the%20Angels&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>$0.24</t>
+          <t>$0.42</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Create X 4/4 white Angel creature tokens with flying. Cycling {2}{W} ({2}{W}, Discard this card: Draw a card.) When you cycle this card, you may pay {X}. If you do, create X 1/1 white Soldier creature tokens.</t>
+          <t>Create X 4/4 white Angel creature tokens with flying. Miracle {X}{W}{W} (You may cast this card for its miracle cost when you draw it if it's the first card you drew this turn.)</t>
         </is>
       </c>
     </row>
@@ -1448,11 +1436,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Divine Visitation</t>
+          <t>Everflowing Chalice</t>
         </is>
       </c>
       <c r="C19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -1465,31 +1453,31 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mythic</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TDC</t>
+          <t>EOC</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Divine%20Visitation&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Everflowing%20Chalice&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>$1.01</t>
+          <t>$0.31</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>If one or more creature tokens would be created under your control, that many 4/4 white Angel creature tokens with flying and vigilance are created instead.</t>
+          <t>Multikicker {2} (You may pay an additional {2} any number of times as you cast this spell.) This artifact enters with a charge counter on it for each time it was kicked. {T}: Add {C} for each charge counter on this artifact.</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1489,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Earth Kingdom Jailer</t>
+          <t>Expel the Interlopers</t>
         </is>
       </c>
       <c r="C20" t="b">
@@ -1513,36 +1501,36 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>Wrath</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>TLA</t>
+          <t>TDC</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Earth%20Kingdom%20Jailer&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Expel%20the%20Interlopers&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>$0.27</t>
+          <t>$0.26</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>When this creature enters, exile up to one target artifact, creature, or enchantment an opponent controls with mana value 3 or greater until this creature leaves the battlefield.</t>
+          <t>Choose a number between 0 and 10. Destroy all creatures with power greater than or equal to the chosen number.</t>
         </is>
       </c>
     </row>
@@ -1554,52 +1542,48 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Eluge, the Shoreless Sea</t>
+          <t>Faerie Mastermind</t>
         </is>
       </c>
       <c r="C21" t="b">
         <v>1</v>
       </c>
       <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Off-theme — makes no tokens, gives no keywords, doesn't support Waterbend; demanding {1}{U}{U}{U} cost with no payoff for the strategy; replaced by Secure the Wastes.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mythic</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>BLB</t>
+          <t>SOC</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Eluge%2C%20the%20Shoreless%20Sea&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Faerie%20Mastermind&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>$4.33</t>
+          <t>$10.52</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Eluge's power and toughness are each equal to the number of Islands you control. Whenever Eluge enters or attacks, put a flood counter on target land. It's an Island in addition to its other types for as long as it has a flood counter on it. The first instant or sorcery spell you cast each turn costs {U} (or {1}) less to cast for each land you control with a flood counter on it.</t>
+          <t>Flash Flying Whenever an opponent draws their second card each turn, you draw a card. {3}{U}: Each player draws a card.</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1595,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Emeria Angel</t>
+          <t>Faramir, Prince of Ithilien</t>
         </is>
       </c>
       <c r="C22" t="b">
@@ -1633,7 +1617,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TDC</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1642,7 +1626,7 @@
         </is>
       </c>
       <c r="J22">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Emeria%20Angel&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Faramir%2C%20Prince%20of%20Ithilien&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K22" t="inlineStr">
@@ -1652,7 +1636,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Flying Landfall — Whenever a land you control enters, you may create a 1/1 white Bird creature token with flying.</t>
+          <t>At the beginning of your end step, choose an opponent. At the beginning of that player's next end step, you draw a card if they didn't attack you that turn. Otherwise, create three 1/1 white Human Soldier creature tokens.</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1648,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Empyrean Eagle</t>
+          <t>Felidar Retreat</t>
         </is>
       </c>
       <c r="C23" t="b">
@@ -1681,7 +1665,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1691,21 +1675,21 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Empyrean%20Eagle&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Felidar%20Retreat&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>$0.29</t>
+          <t>$1.26</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Flying Other creatures you control with flying get +1/+1.</t>
+          <t>Landfall — Whenever a land you control enters, choose one — • Create a 2/2 white Cat Beast creature token. • Put a +1/+1 counter on each creature you control. Those creatures gain vigilance until end of turn.</t>
         </is>
       </c>
     </row>
@@ -1717,11 +1701,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Entreat the Angels</t>
+          <t>Fell the Mighty</t>
         </is>
       </c>
       <c r="C24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
@@ -1729,36 +1713,36 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Wrath</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mythic</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DSC</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Entreat%20the%20Angels&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Fell%20the%20Mighty&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>$0.39</t>
+          <t>$0.36</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Create X 4/4 white Angel creature tokens with flying. Miracle {X}{W}{W} (You may cast this card for its miracle cost when you draw it if it's the first card you drew this turn.)</t>
+          <t>Destroy all creatures with power greater than target creature's power.</t>
         </is>
       </c>
     </row>
@@ -1770,20 +1754,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Essence Scatter</t>
+          <t>Finale of Glory</t>
         </is>
       </c>
       <c r="C25" t="b">
         <v>1</v>
       </c>
       <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Narrow creature-only counter redundant with existing removal suite; replaced by Counterspell for a hard counter with no restrictions.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>On Theme</t>
@@ -1791,12 +1771,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Mythic</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>CLU</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1805,17 +1785,17 @@
         </is>
       </c>
       <c r="J25">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Essence%20Scatter&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Finale%20of%20Glory&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>$0.21</t>
+          <t>$2.45</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Counter target creature spell.</t>
+          <t>Create X 2/2 white Soldier creature tokens with vigilance. If X is 10 or more, also create X 4/4 white Angel creature tokens with flying and vigilance.</t>
         </is>
       </c>
     </row>
@@ -1827,52 +1807,48 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ethereal Investigator</t>
+          <t>Ghostly Prison</t>
         </is>
       </c>
       <c r="C26" t="b">
         <v>1</v>
       </c>
       <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Clue token draw is slow and the spirit ETB is incidental; replaced by Faerie Mastermind which draws off every opponent's card draw.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>SOC</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Ethereal%20Investigator&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Ghostly%20Prison&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>$0.35</t>
+          <t>$5.29</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Flying When this creature enters, investigate X times, where X is the number of opponents you have. (To investigate, create a Clue token. It's an artifact with "{2}, Sacrifice this token: Draw a card.") Whenever you draw your second card each turn, create a 1/1 white Spirit creature token with flying.</t>
+          <t>Creatures can't attack you unless their controller pays {2} for each creature they control that's attacking you.</t>
         </is>
       </c>
     </row>
@@ -1884,33 +1860,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Everflowing Chalice</t>
+          <t>Glacial Fortress</t>
         </is>
       </c>
       <c r="C27" t="b">
         <v>1</v>
       </c>
       <c r="D27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Starts at 0 useful mana and requires repeated investment to scale; replaced by Whirlwind of Thought and Alhammarret's Archive.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Lands</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>EOC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1919,17 +1891,17 @@
         </is>
       </c>
       <c r="J27">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Everflowing%20Chalice&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Glacial%20Fortress&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>$0.36</t>
+          <t>$0.30</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Multikicker {2} (You may pay an additional {2} any number of times as you cast this spell.) This artifact enters with a charge counter on it for each time it was kicked. {T}: Add {C} for each charge counter on this artifact.</t>
+          <t>This land enters tapped unless you control a Plains or an Island. {T}: Add {W} or {U}.</t>
         </is>
       </c>
     </row>
@@ -1941,11 +1913,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Faerie Mastermind</t>
+          <t>Grasp of Fate</t>
         </is>
       </c>
       <c r="C28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
@@ -1953,7 +1925,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Card Advantage</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1963,26 +1935,26 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SOC</t>
+          <t>WHO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Faerie%20Mastermind&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Grasp%20of%20Fate&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>$10.73</t>
+          <t>$0.37</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Flash Flying Whenever an opponent draws their second card each turn, you draw a card. {3}{U}: Each player draws a card.</t>
+          <t>When this enchantment enters, for each opponent, exile up to one target nonland permanent that player controls until this enchantment leaves the battlefield. (Those permanents return under their owners' control.)</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1966,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Favorable Winds</t>
+          <t>Hedron Archive</t>
         </is>
       </c>
       <c r="C29" t="b">
@@ -2006,7 +1978,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2016,26 +1988,26 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SCD</t>
+          <t>BLC</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Favorable%20Winds&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Hedron%20Archive&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$0.34</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Creatures you control with flying get +1/+1.</t>
+          <t>{T}: Add {C}{C}. {2}, {T}, Sacrifice this artifact: Draw two cards.</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2019,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Felidar Retreat</t>
+          <t>Idol of Oblivion</t>
         </is>
       </c>
       <c r="C30" t="b">
@@ -2069,26 +2041,26 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>PLST</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Felidar%20Retreat&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Idol%20of%20Oblivion&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>$1.17</t>
+          <t>$1.11</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Landfall — Whenever a land you control enters, choose one — • Create a 2/2 white Cat Beast creature token. • Put a +1/+1 counter on each creature you control. Those creatures gain vigilance until end of turn.</t>
+          <t>{T}: Draw a card. Activate only if you created a token this turn. {8}, {T}, Sacrifice this artifact: Create a 10/10 colorless Eldrazi creature token.</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2072,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fell the Mighty</t>
+          <t>Idyllic Beachfront</t>
         </is>
       </c>
       <c r="C31" t="b">
@@ -2112,36 +2084,36 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wrath</t>
+          <t>Lands</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>FIC</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J31">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Fell%20the%20Mighty&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Idyllic%20Beachfront&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>$0.27</t>
+          <t>$0.23</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Destroy all creatures with power greater than target creature's power.</t>
+          <t>({T}: Add {W} or {U}.) This land enters tapped.</t>
         </is>
       </c>
     </row>
@@ -2153,20 +2125,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fire Nation Warship</t>
+          <t>Intangible Virtue</t>
         </is>
       </c>
       <c r="C32" t="b">
         <v>1</v>
       </c>
       <c r="D32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Off-theme vehicle in a Water Tribe deck; crew cost competes with Waterbend tapping.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>On Theme</t>
@@ -2179,26 +2147,26 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>TLA</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Fire%20Nation%20Warship&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Intangible%20Virtue&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>$0.17</t>
+          <t>$0.27</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Reach When this Vehicle dies, create a Clue token. (It's an artifact with "{2}, Sacrifice this token: Draw a card.") Crew 2 (Tap any number of creatures you control with total power 2 or more: This Vehicle becomes an artifact creature until end of turn.)</t>
+          <t>Creature tokens you control get +1/+1 and have vigilance.</t>
         </is>
       </c>
     </row>
@@ -2210,11 +2178,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ghostly Prison</t>
+          <t>Irrigated Farmland</t>
         </is>
       </c>
       <c r="C33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" t="b">
         <v>0</v>
@@ -2222,48 +2190,48 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>Lands</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SOC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J33">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Ghostly%20Prison&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Irrigated%20Farmland&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>$4.24</t>
+          <t>$0.38</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Creatures can't attack you unless their controller pays {2} for each creature they control that's attacking you.</t>
+          <t>({T}: Add {W} or {U}.) This land enters tapped. Cycling {2} ({2}, Discard this card: Draw a card.)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="270" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Glacial Fortress</t>
+          <t>Island</t>
         </is>
       </c>
       <c r="C34" t="b">
@@ -2280,12 +2248,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>EOC</t>
+          <t>HOB</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2294,17 +2262,17 @@
         </is>
       </c>
       <c r="J34">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Glacial%20Fortress&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Island&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>$0.38</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>This land enters tapped unless you control a Plains or an Island. {T}: Add {W} or {U}.</t>
+          <t>({T}: Add {U}.)</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2284,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hedron Archive</t>
+          <t>Katara, Water Tribe's Hope</t>
         </is>
       </c>
       <c r="C35" t="b">
@@ -2328,36 +2296,36 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Card Advantage</t>
+          <t>On Theme</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>BLC</t>
+          <t>TLA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Hedron%20Archive&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Katara%2C%20Water%20Tribe%27s%20Hope&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>$0.29</t>
+          <t>$0.49</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>{T}: Add {C}{C}. {2}, {T}, Sacrifice this artifact: Draw two cards.</t>
+          <t>Vigilance When Katara enters, create a 1/1 white Ally creature token. Waterbend {X}: Creatures you control have base power and toughness X/X until end of turn. X can't be 0. Activate only during your turn. (While paying a waterbend cost, you can tap your artifacts and creatures to help. Each one pays for {1}.)</t>
         </is>
       </c>
     </row>
@@ -2369,23 +2337,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Idol of Oblivion</t>
+          <t>Keeper of the Accord</t>
         </is>
       </c>
       <c r="C36" t="b">
         <v>1</v>
       </c>
       <c r="D36" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Too conditional — requires creating tokens that same turn; replaced by Smuggler's Share which draws every opponent's turn passively.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2395,26 +2359,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>TDC</t>
+          <t>PIP</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J36">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Idol%20of%20Oblivion&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Keeper%20of%20the%20Accord&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>$0.93</t>
+          <t>$0.54</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>{T}: Draw a card. Activate only if you created a token this turn. {8}, {T}, Sacrifice this artifact: Create a 10/10 colorless Eldrazi creature token.</t>
+          <t>At the beginning of each opponent's end step, if that player controls more creatures than you, create a 1/1 white Soldier creature token. At the beginning of each opponent's end step, if that player controls more lands than you, you may search your library for a basic Plains card, put it onto the battlefield tapped, then shuffle.</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2390,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Idyllic Beachfront</t>
+          <t>Loyal Unicorn</t>
         </is>
       </c>
       <c r="C37" t="b">
@@ -2438,36 +2402,36 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lands</t>
+          <t>On Theme</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>CMM</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J37">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Idyllic%20Beachfront&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Loyal%20Unicorn&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>$0.31</t>
+          <t>$0.26</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>({T}: Add {W} or {U}.) This land enters tapped.</t>
+          <t>Vigilance Lieutenant — At the beginning of combat on your turn, if you control your commander, prevent all combat damage that would be dealt to creatures you control this turn. Other creatures you control gain vigilance until end of turn.</t>
         </is>
       </c>
     </row>
@@ -2479,33 +2443,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Inspired Insurgent</t>
+          <t>Mind Stone</t>
         </is>
       </c>
       <c r="C38" t="b">
         <v>1</v>
       </c>
       <c r="D38" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Strictly redundant with Curious Farm Animals — both sacrifice to destroy artifacts/enchantments; Curious Farm Animals is cheaper and a 1/1 for Tetsuko synergy; replaced by Rootborn Defenses.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>SOC</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2514,17 +2474,17 @@
         </is>
       </c>
       <c r="J38">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Inspired%20Insurgent&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Mind%20Stone&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.32</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>{1}, Sacrifice this creature: Destroy target artifact or enchantment.</t>
+          <t>{T}: Add {C}. {1}, {T}, Sacrifice this artifact: Draw a card.</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2496,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Intangible Virtue</t>
+          <t>Mister Fantastic, Reed Richards</t>
         </is>
       </c>
       <c r="C39" t="b">
@@ -2548,7 +2508,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2558,26 +2518,26 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>MSH</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J39">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Intangible%20Virtue&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Mister%20Fantastic%2C%20Reed%20Richards&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>$0.45</t>
+          <t>$0.28</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Creature tokens you control get +1/+1 and have vigilance.</t>
+          <t>Reach Whenever one or more tokens you control enter, you may draw a card.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2549,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Irrigated Farmland</t>
+          <t>Negate</t>
         </is>
       </c>
       <c r="C40" t="b">
@@ -2601,48 +2561,48 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lands</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>EOC</t>
+          <t>TMT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Irrigated%20Farmland&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Negate&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>$0.23</t>
+          <t>$0.36</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>({T}: Add {W} or {U}.) This land enters tapped. Cycling {2} ({2}, Discard this card: Draw a card.)</t>
+          <t>Counter target noncreature spell.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="270" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Island</t>
+          <t>North Pole Gates</t>
         </is>
       </c>
       <c r="C41" t="b">
@@ -2664,7 +2624,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>TLA</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2673,17 +2633,17 @@
         </is>
       </c>
       <c r="J41">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Island&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=North%20Pole%20Gates&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>$0.16</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>({T}: Add {U}.)</t>
+          <t>This land enters tapped. {T}: Add {W} or {U}. {4}, {T}, Sacrifice this land: Draw a card.</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2655,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Journey to Nowhere</t>
+          <t>Odric, Lunarch Marshal</t>
         </is>
       </c>
       <c r="C42" t="b">
@@ -2707,36 +2667,36 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>On Theme</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PLST</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J42">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Journey%20to%20Nowhere&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Odric%2C%20Lunarch%20Marshal&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>$0.19</t>
+          <t>$1.39</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>When this enchantment enters, exile target creature. When this enchantment leaves the battlefield, return the exiled card to the battlefield under its owner's control.</t>
+          <t>At the beginning of each combat, creatures you control gain first strike until end of turn if a creature you control has first strike. The same is true for flying, deathtouch, double strike, haste, hexproof, indestructible, lifelink, menace, reach, skulk, trample, and vigilance.</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2708,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Katara, Water Tribe's Hope</t>
+          <t>Ornithopter of Paradise</t>
         </is>
       </c>
       <c r="C43" t="b">
@@ -2760,26 +2720,26 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>TLA</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Katara%2C%20Water%20Tribe%27s%20Hope&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Ornithopter%20of%20Paradise&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K43" t="inlineStr">
@@ -2789,7 +2749,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Vigilance When Katara enters, create a 1/1 white Ally creature token. Waterbend {X}: Creatures you control have base power and toughness X/X until end of turn. X can't be 0. Activate only during your turn. (While paying a waterbend cost, you can tap your artifacts and creatures to help. Each one pays for {1}.)</t>
+          <t>Flying {T}: Add one mana of any color.</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2761,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Keeper of the Accord</t>
+          <t>Path of the Ghosthunter</t>
         </is>
       </c>
       <c r="C44" t="b">
@@ -2813,7 +2773,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>On Theme</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2823,26 +2783,26 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>PIP</t>
+          <t>MOC</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Keeper%20of%20the%20Accord&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Path%20of%20the%20Ghosthunter&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>$0.43</t>
+          <t>$0.27</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>At the beginning of each opponent's end step, if that player controls more creatures than you, create a 1/1 white Soldier creature token. At the beginning of each opponent's end step, if that player controls more lands than you, you may search your library for a basic Plains card, put it onto the battlefield tapped, then shuffle.</t>
+          <t>Create X 1/1 white Spirit creature tokens with flying. Will of the Planeswalkers — Starting with you, each player votes for planeswalk or chaos. If planeswalk gets more votes, planeswalk. If chaos gets more votes or the vote is tied, chaos ensues.</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2814,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Loyal Unicorn</t>
+          <t>Path to Exile</t>
         </is>
       </c>
       <c r="C45" t="b">
@@ -2866,7 +2826,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2876,83 +2836,79 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CMM</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Loyal%20Unicorn&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Path%20to%20Exile&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>$0.19</t>
+          <t>$1.11</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Vigilance Lieutenant — At the beginning of combat on your turn, if you control your commander, prevent all combat damage that would be dealt to creatures you control this turn. Other creatures you control gain vigilance until end of turn.</t>
+          <t>Exile target creature. Its controller may search their library for a basic land card, put that card onto the battlefield tapped, then shuffle.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="270" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Luminarch Ascension</t>
+          <t>Plains</t>
         </is>
       </c>
       <c r="C46" t="b">
         <v>1</v>
       </c>
       <c r="D46" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Don't own physical copy ($12.70); replaced by Entreat the Angels for equivalent flying angel token generation at budget price.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Lands</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>HOB</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J46">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Luminarch%20Ascension&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Plains&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>$12.70</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>At the beginning of each opponent's end step, if you didn't lose life this turn, you may put a quest counter on this enchantment. (Damage causes loss of life.) {1}{W}: Create a 4/4 white Angel creature token with flying. Activate only if this enchantment has four or more quest counters on it.</t>
+          <t>({T}: Add {W}.)</t>
         </is>
       </c>
     </row>
@@ -2964,11 +2920,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Military Intelligence</t>
+          <t>Port Town</t>
         </is>
       </c>
       <c r="C47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" t="b">
         <v>0</v>
@@ -2976,36 +2932,36 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Card Advantage</t>
+          <t>Lands</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>PLST</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J47">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Military%20Intelligence&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Port%20Town&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>$0.36</t>
+          <t>$0.25</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Whenever you attack with two or more creatures, draw a card.</t>
+          <t>As this land enters, you may reveal a Plains or Island card from your hand. If you don't, this land enters tapped. {T}: Add {W} or {U}.</t>
         </is>
       </c>
     </row>
@@ -3017,7 +2973,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mind Stone</t>
+          <t>Prairie Stream</t>
         </is>
       </c>
       <c r="C48" t="b">
@@ -3029,36 +2985,36 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Card Advantage</t>
+          <t>Lands</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SOC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J48">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Mind%20Stone&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Prairie%20Stream&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>$0.27</t>
+          <t>$0.28</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>{T}: Add {C}. {1}, {T}, Sacrifice this artifact: Draw a card.</t>
+          <t>({T}: Add {W} or {U}.) This land enters tapped unless you control two or more basic lands.</t>
         </is>
       </c>
     </row>
@@ -3070,11 +3026,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Monastery Mentor</t>
+          <t>Prince Imrahil the Fair</t>
         </is>
       </c>
       <c r="C49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="b">
         <v>0</v>
@@ -3087,31 +3043,31 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Mythic</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>TDC</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Monastery%20Mentor&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Prince%20Imrahil%20the%20Fair&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>$0.53</t>
+          <t>$0.18</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Prowess (Whenever you cast a noncreature spell, this creature gets +1/+1 until end of turn.) Whenever you cast a noncreature spell, create a 1/1 white Monk creature token with prowess.</t>
+          <t>Whenever you draw your second card each turn, create a 1/1 white Human Soldier creature token.</t>
         </is>
       </c>
     </row>
@@ -3123,11 +3079,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Monologue Tax</t>
+          <t>Prismatic Lens</t>
         </is>
       </c>
       <c r="C50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" t="b">
         <v>0</v>
@@ -3140,31 +3096,31 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SOC</t>
+          <t>PLST</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Monologue%20Tax&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Prismatic%20Lens&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>$2.06</t>
+          <t>$0.31</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Whenever an opponent casts their second spell each turn, you create a Treasure token.</t>
+          <t>{T}: Add {C}. {1}, {T}: Add one mana of any color.</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3132,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Negate</t>
+          <t>Propaganda</t>
         </is>
       </c>
       <c r="C51" t="b">
@@ -3193,31 +3149,31 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>TMT</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J51">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Negate&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Propaganda&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>$0.09</t>
+          <t>$1.97</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Counter target noncreature spell.</t>
+          <t>Creatures can't attack you unless their controller pays {2} for each creature they control that's attacking you.</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3185,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>North Pole Gates</t>
+          <t>PuPu UFO</t>
         </is>
       </c>
       <c r="C52" t="b">
@@ -3241,36 +3197,36 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lands</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>TLA</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J52">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=North%20Pole%20Gates&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=PuPu%20UFO&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>$0.22</t>
+          <t>$0.53</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>This land enters tapped. {T}: Add {W} or {U}. {4}, {T}, Sacrifice this land: Draw a card.</t>
+          <t>Flying {T}: You may put a land card from your hand onto the battlefield. {3}: Until end of turn, this creature's base power becomes equal to the number of Towns you control.</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3238,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Odric, Lunarch Marshal</t>
+          <t>Pull from Tomorrow</t>
         </is>
       </c>
       <c r="C53" t="b">
@@ -3294,7 +3250,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3304,26 +3260,26 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>SOC</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J53">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Odric%2C%20Lunarch%20Marshal&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Pull%20from%20Tomorrow&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>$1.11</t>
+          <t>$0.29</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>At the beginning of each combat, creatures you control gain first strike until end of turn if a creature you control has first strike. The same is true for flying, deathtouch, double strike, haste, hexproof, indestructible, lifelink, menace, reach, skulk, trample, and vigilance.</t>
+          <t>Draw X cards, then discard a card.</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3291,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ornithopter of Paradise</t>
+          <t>Reconnaissance Mission</t>
         </is>
       </c>
       <c r="C54" t="b">
@@ -3347,36 +3303,36 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J54">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Ornithopter%20of%20Paradise&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Reconnaissance%20Mission&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>$0.37</t>
+          <t>$0.89</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Flying {T}: Add one mana of any color.</t>
+          <t>Whenever a creature you control deals combat damage to a player, you may draw a card. Cycling {2} ({2}, Discard this card: Draw a card.)</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3344,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Path to Exile</t>
+          <t>Refute</t>
         </is>
       </c>
       <c r="C55" t="b">
@@ -3405,43 +3361,43 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SOC</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J55">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Path%20to%20Exile&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Refute&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>$1.06</t>
+          <t>$0.26</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Exile target creature. Its controller may search their library for a basic land card, put that card onto the battlefield tapped, then shuffle.</t>
+          <t>Counter target spell. Draw a card, then discard a card.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="270" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Plains</t>
+          <t>Secure the Wastes</t>
         </is>
       </c>
       <c r="C56" t="b">
@@ -3453,36 +3409,36 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lands</t>
+          <t>On Theme</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>PIP</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Plains&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Secure%20the%20Wastes&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>$0.60</t>
+          <t>$2.71</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>({T}: Add {W}.)</t>
+          <t>Create X 1/1 white Warrior creature tokens.</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3450,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Port Town</t>
+          <t>Shorikai, Genesis Engine</t>
         </is>
       </c>
       <c r="C57" t="b">
@@ -3506,36 +3462,36 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lands</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Mythic</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J57">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Port%20Town&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Shorikai%2C%20Genesis%20Engine&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>$0.13</t>
+          <t>$2.32</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>As this land enters, you may reveal a Plains or Island card from your hand. If you don't, this land enters tapped. {T}: Add {W} or {U}.</t>
+          <t>{1}, {T}: Draw two cards, then discard a card. Create a 1/1 colorless Pilot creature token with "This token crews Vehicles as though its power were 2 greater." Crew 8 (Tap any number of creatures you control with total power 8 or more: This Vehicle becomes an artifact creature until end of turn.)</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3503,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Prairie Stream</t>
+          <t>Silver Scrutiny</t>
         </is>
       </c>
       <c r="C58" t="b">
@@ -3559,7 +3515,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lands</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3569,26 +3525,26 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>PDMU</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J58">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Prairie%20Stream&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Silver%20Scrutiny&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.37</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>({T}: Add {W} or {U}.) This land enters tapped unless you control two or more basic lands.</t>
+          <t>You may cast this spell as though it had flash if X is 3 or less. Draw X cards.</t>
         </is>
       </c>
     </row>
@@ -3600,11 +3556,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Prava of the Steel Legion</t>
+          <t>Sol Ring</t>
         </is>
       </c>
       <c r="C59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" t="b">
         <v>0</v>
@@ -3612,7 +3568,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3622,26 +3578,26 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>PLST</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Prava%20of%20the%20Steel%20Legion&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Sol%20Ring&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>$0.39</t>
+          <t>$1.15</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>During your turn, creature tokens you control get +1/+4. {3}{W}: Create a 1/1 white Soldier creature token. Partner (You can have two commanders if both have partner.)</t>
+          <t>{T}: Add {C}{C}.</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3609,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Precinct Captain</t>
+          <t>Spirit Water Revival</t>
         </is>
       </c>
       <c r="C60" t="b">
@@ -3665,7 +3621,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3675,26 +3631,26 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>TLA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J60">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Precinct%20Captain&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Spirit%20Water%20Revival&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>$0.29</t>
+          <t>$0.77</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>First strike Whenever this creature deals combat damage to a player, create a 1/1 white Soldier creature token.</t>
+          <t>As an additional cost to cast this spell, you may waterbend {6}. (While paying a waterbend cost, you can tap your artifacts and creatures to help. Each one pays for {1}.) Draw two cards. If this spell's additional cost was paid, instead shuffle your graveyard into your library, draw seven cards, and you have no maximum hand size for the rest of the game. Exile Spirit Water Revival.</t>
         </is>
       </c>
     </row>
@@ -3706,20 +3662,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Prismatic Lens</t>
+          <t>Storm Herd</t>
         </is>
       </c>
       <c r="C61" t="b">
         <v>1</v>
       </c>
       <c r="D61" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Worst rate in the ramp package — 2 mana for 1 colorless; replaced by Monologue Tax for reactive Treasure generation.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>On Theme</t>
@@ -3727,7 +3679,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3737,21 +3689,21 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J61">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Prismatic%20Lens&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Storm%20Herd&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$3.06</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>{T}: Add {C}. {1}, {T}: Add one mana of any color.</t>
+          <t>Create X 1/1 white Pegasus creature tokens with flying, where X is your life total.</t>
         </is>
       </c>
     </row>
@@ -3763,11 +3715,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Propaganda</t>
+          <t>Stroke of Midnight</t>
         </is>
       </c>
       <c r="C62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="b">
         <v>0</v>
@@ -3785,7 +3737,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>TDC</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3794,17 +3746,17 @@
         </is>
       </c>
       <c r="J62">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Propaganda&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Stroke%20of%20Midnight&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>$3.54</t>
+          <t>$0.33</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Creatures can't attack you unless their controller pays {2} for each creature they control that's attacking you.</t>
+          <t>Destroy target nonland permanent. Its controller creates a 1/1 white Human creature token.</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3768,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Reconnaissance Mission</t>
+          <t>Talisman of Progress</t>
         </is>
       </c>
       <c r="C63" t="b">
@@ -3828,7 +3780,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Card Advantage</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3838,26 +3790,26 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>WOC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J63">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Reconnaissance%20Mission&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Talisman%20of%20Progress&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>$2.88</t>
+          <t>$0.44</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Whenever a creature you control deals combat damage to a player, you may draw a card. Cycling {2} ({2}, Discard this card: Draw a card.)</t>
+          <t>{T}: Add {C}. {T}: Add {W} or {U}. This artifact deals 1 damage to you.</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3821,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Refute</t>
+          <t>Talrand, Sky Summoner</t>
         </is>
       </c>
       <c r="C64" t="b">
@@ -3881,36 +3833,36 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>On Theme</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>OTC</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J64">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Refute&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Talrand%2C%20Sky%20Summoner&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>$0.24</t>
+          <t>$0.77</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Counter target spell. Draw a card, then discard a card.</t>
+          <t>Whenever you cast an instant or sorcery spell, create a 2/2 blue Drake creature token with flying.</t>
         </is>
       </c>
     </row>
@@ -3922,23 +3874,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Retrofitter Foundry</t>
+          <t>Teferi's Ageless Insight</t>
         </is>
       </c>
       <c r="C65" t="b">
         <v>1</v>
       </c>
       <c r="D65" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Niche artifact token conversion without a steady Gnome/Construct supply; replaced by Monastery Mentor for spell-triggered token generation.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3948,26 +3896,26 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>J25</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J65">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Retrofitter%20Foundry&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Teferi%27s%20Ageless%20Insight&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>$0.32</t>
+          <t>$3.06</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>{3}: Untap this artifact. {2}, {T}: Create a 1/1 colorless Servo artifact creature token. {1}, {T}, Sacrifice a Servo: Create a 1/1 colorless Thopter artifact creature token with flying. {T}, Sacrifice a Thopter: Create a 4/4 colorless Construct artifact creature token.</t>
+          <t>If you would draw a card except the first one you draw in each of your draw steps, draw two cards instead.</t>
         </is>
       </c>
     </row>
@@ -3979,23 +3927,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rhystic Study</t>
+          <t>Temple of Enlightenment</t>
         </is>
       </c>
       <c r="C66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Don't own physical copy ($60+); replaced by Teferi's Ageless Insight which doubles all non-first draws for $3 vs $11 Archive.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Lands</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4005,26 +3949,26 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>J22</t>
+          <t>EOC</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J66">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Rhystic%20Study&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Temple%20of%20Enlightenment&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>$69.05</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Whenever an opponent casts a spell, you may draw a card unless that player pays {1}.</t>
+          <t>This land enters tapped. When this land enters, scry 1. (Look at the top card of your library. You may put that card on the bottom.) {T}: Add {W} or {U}.</t>
         </is>
       </c>
     </row>
@@ -4036,11 +3980,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rootborn Defenses</t>
+          <t>The Council of Four</t>
         </is>
       </c>
       <c r="C67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" t="b">
         <v>0</v>
@@ -4048,36 +3992,36 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>CLB</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J67">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Rootborn%20Defenses&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=The%20Council%20of%20Four&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>$0.24</t>
+          <t>$1.82</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Populate. Creatures you control gain indestructible until end of turn. (To populate, create a token that's a copy of a creature token you control.)</t>
+          <t>Whenever a player draws their second card during their turn, you draw a card. Whenever a player casts their second spell during their turn, you create a 2/2 white Knight creature token.</t>
         </is>
       </c>
     </row>
@@ -4089,11 +4033,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Secure the Wastes</t>
+          <t>The Unagi of Kyoshi Island</t>
         </is>
       </c>
       <c r="C68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" t="b">
         <v>0</v>
@@ -4101,7 +4045,7 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>On Theme</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4111,26 +4055,26 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>PIP</t>
+          <t>TLA</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J68">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Secure%20the%20Wastes&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=The%20Unagi%20of%20Kyoshi%20Island&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>$4.26</t>
+          <t>$1.22</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Create X 1/1 white Warrior creature tokens.</t>
+          <t>Flash Ward—Waterbend {4}. (Whenever this creature becomes the target of a spell or ability an opponent controls, counter it unless that player pays {4}. They can tap their artifacts and creatures to help. Each one pays for {1}.) Whenever an opponent draws their second card each turn, you draw two cards.</t>
         </is>
       </c>
     </row>
@@ -4142,20 +4086,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Skeleton Key</t>
+          <t>The Walls of Ba Sing Se</t>
         </is>
       </c>
       <c r="C69" t="b">
         <v>1</v>
       </c>
       <c r="D69" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Skulk and loot are useful early but become marginal once the board is established; replaced by Prava of the Steel Legion for reactive blocking token generation.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>On Theme</t>
@@ -4163,31 +4103,31 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Mythic</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SOI</t>
+          <t>TLA</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J69">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Skeleton%20Key&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=The%20Walls%20of%20Ba%20Sing%20Se&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>$0.29</t>
+          <t>$22.99</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Equipped creature has skulk. (It can't be blocked by creatures with greater power.) Whenever equipped creature deals combat damage to a player, you may draw a card. If you do, discard a card. Equip {2}</t>
+          <t>Defender Other permanents you control have indestructible.</t>
         </is>
       </c>
     </row>
@@ -4199,11 +4139,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Skullclamp</t>
+          <t>Thought Vessel</t>
         </is>
       </c>
       <c r="C70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" t="b">
         <v>0</v>
@@ -4211,7 +4151,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Card Advantage</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4221,26 +4161,26 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J70">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Skullclamp&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Thought%20Vessel&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>$6.24</t>
+          <t>$1.74</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Equipped creature gets +1/-1. Whenever equipped creature dies, draw two cards. Equip {1}</t>
+          <t>You have no maximum hand size. {T}: Add {C}.</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4192,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Skycat Sovereign</t>
+          <t>Thraben Doomsayer</t>
         </is>
       </c>
       <c r="C71" t="b">
@@ -4274,26 +4214,26 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SCD</t>
+          <t>C20</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J71">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Skycat%20Sovereign&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Thraben%20Doomsayer&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>$0.23</t>
+          <t>$0.40</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Flying This creature gets +1/+1 for each other creature you control with flying. {2}{W}{U}: Create a 1/1 white Cat Bird creature token with flying.</t>
+          <t>{T}: Create a 1/1 white Human creature token. Fateful hour — As long as you have 5 or less life, other creatures you control get +2/+2.</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4245,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Skycloud Expanse</t>
+          <t>Thriving Heath</t>
         </is>
       </c>
       <c r="C72" t="b">
@@ -4322,12 +4262,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>EOC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4336,17 +4276,17 @@
         </is>
       </c>
       <c r="J72">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Skycloud%20Expanse&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Thriving%20Heath&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.24</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>{1}, {T}: Add {W}{U}.</t>
+          <t>This land enters tapped. As it enters, choose a color other than white. {T}: Add {W} or one mana of the chosen color.</t>
         </is>
       </c>
     </row>
@@ -4358,11 +4298,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Smuggler's Share</t>
+          <t>Thriving Isle</t>
         </is>
       </c>
       <c r="C73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" t="b">
         <v>0</v>
@@ -4370,36 +4310,36 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Card Advantage</t>
+          <t>Lands</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J73">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Smuggler%27s%20Share&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Thriving%20Isle&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>$9.21</t>
+          <t>$0.21</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>At the beginning of each end step, draw a card for each opponent who drew two or more cards this turn, then create a Treasure token for each opponent who had two or more lands enter the battlefield under their control this turn.</t>
+          <t>This land enters tapped. As it enters, choose a color other than blue. {T}: Add {U} or one mana of the chosen color.</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4351,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sol Ring</t>
+          <t>Tocasia's Welcome</t>
         </is>
       </c>
       <c r="C74" t="b">
@@ -4423,12 +4363,12 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4438,21 +4378,21 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J74">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Sol%20Ring&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Tocasia%27s%20Welcome&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>$1.22</t>
+          <t>$0.61</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>{T}: Add {C}{C}.</t>
+          <t>Whenever one or more creatures you control with mana value 3 or less enter, draw a card. This ability triggers only once each turn.</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4404,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Storm Herd</t>
+          <t>Venser's Journal</t>
         </is>
       </c>
       <c r="C75" t="b">
@@ -4486,26 +4426,26 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>PLST</t>
+          <t>C21</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J75">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Storm%20Herd&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Venser%27s%20Journal&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>$2.71</t>
+          <t>$9.24</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Create X 1/1 white Pegasus creature tokens with flying, where X is your life total.</t>
+          <t>You have no maximum hand size. At the beginning of your upkeep, you gain 1 life for each card in your hand.</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4457,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Stormbeacon Blade</t>
+          <t>Verge Rangers</t>
         </is>
       </c>
       <c r="C76" t="b">
@@ -4534,31 +4474,31 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>TDM</t>
+          <t>DSC</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J76">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Stormbeacon%20Blade&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Verge%20Rangers&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>$0.23</t>
+          <t>$0.32</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Equipped creature gets +3/+0. Whenever equipped creature attacks, draw a card if you control three or more attacking creatures. Equip {2} ({2}: Attach to target creature you control. Equip only as a sorcery.)</t>
+          <t>First strike You may look at the top card of your library any time. As long as an opponent controls more lands than you, you may play lands from the top of your library. (You can play a land this way only if you have an available land play remaining.)</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4510,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Stroke of Midnight</t>
+          <t>Willie Lumpkin, Postman</t>
         </is>
       </c>
       <c r="C77" t="b">
@@ -4582,965 +4522,52 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>Card Advantage</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>TDC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Stroke%20of%20Midnight&amp;format=image&amp;version=normal")</f>
+        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Willie%20Lumpkin%2C%20Postman&amp;format=image&amp;version=normal")</f>
         <v/>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>$0.36</t>
+          <t>$1.64</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Destroy target nonland permanent. Its controller creates a 1/1 white Human creature token.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="270" customHeight="1">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Swiftfoot Boots</t>
-        </is>
-      </c>
-      <c r="C78" t="b">
-        <v>1</v>
-      </c>
-      <c r="D78" t="b">
-        <v>0</v>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>On Theme</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>FIC</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J78">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Swiftfoot%20Boots&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>$1.90</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Equipped creature has hexproof and haste. (It can't be the target of spells or abilities your opponents control. It can attack and {T} no matter when it came under your control.) Equip {1} ({1}: Attach to target creature you control. Equip only as a sorcery.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="270" customHeight="1">
+          <t>Willie Lumpkin can't be blocked. Whenever Willie Lumpkin deals combat damage to an opponent, you draw a card and that player may draw a card. If they do, that player can't attack you or permanents you control during their next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Talisman of Progress</t>
-        </is>
-      </c>
-      <c r="C79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" t="b">
-        <v>0</v>
-      </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>FIC</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J79">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Talisman%20of%20Progress&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>$0.35</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>{T}: Add {C}. {T}: Add {W} or {U}. This artifact deals 1 damage to you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="270" customHeight="1">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Talrand, Sky Summoner</t>
-        </is>
-      </c>
-      <c r="C80" t="b">
-        <v>0</v>
-      </c>
-      <c r="D80" t="b">
-        <v>0</v>
-      </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>On Theme</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>OTC</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J80">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Talrand%2C%20Sky%20Summoner&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>$0.81</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Whenever you cast an instant or sorcery spell, create a 2/2 blue Drake creature token with flying.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="270" customHeight="1">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Team Avatar</t>
-        </is>
-      </c>
-      <c r="C81" t="b">
-        <v>1</v>
-      </c>
-      <c r="D81" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Attack-alone condition directly contradicts the go-wide strategy; never want to attack with a single creature in this deck.</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>On Theme</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>TLA</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J81">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Team%20Avatar&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>$0.14</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Whenever a creature you control attacks alone, it gets +X/+X until end of turn, where X is the number of creatures you control. {2}{W}, Discard this card: It deals damage equal to the number of creatures you control to target creature.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="270" customHeight="1">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Teferi's Ageless Insight</t>
-        </is>
-      </c>
-      <c r="C82" t="b">
-        <v>0</v>
-      </c>
-      <c r="D82" t="b">
-        <v>0</v>
-      </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Card Advantage</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>J25</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J82">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Teferi%27s%20Ageless%20Insight&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>$4.75</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>If you would draw a card except the first one you draw in each of your draw steps, draw two cards instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="270" customHeight="1">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Temple of Enlightenment</t>
-        </is>
-      </c>
-      <c r="C83" t="b">
-        <v>1</v>
-      </c>
-      <c r="D83" t="b">
-        <v>0</v>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Lands</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>EOC</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J83">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Temple%20of%20Enlightenment&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>$0.29</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>This land enters tapped. When this land enters, scry 1. (Look at the top card of your library. You may put that card on the bottom.) {T}: Add {W} or {U}.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="270" customHeight="1">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Tetsuko Umezawa, Fugitive</t>
-        </is>
-      </c>
-      <c r="C84" t="b">
-        <v>1</v>
-      </c>
-      <c r="D84" t="b">
-        <v>0</v>
-      </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>On Theme</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>BLC</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J84">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Tetsuko%20Umezawa%2C%20Fugitive&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>$0.29</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Creatures you control with power or toughness 1 or less can't be blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="270" customHeight="1">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>The Battle of Bywater</t>
-        </is>
-      </c>
-      <c r="C85" t="b">
-        <v>1</v>
-      </c>
-      <c r="D85" t="b">
-        <v>0</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Wrath</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>LTR</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J85">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=The%20Battle%20of%20Bywater&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>$3.52</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Destroy all creatures with power 3 or greater. Then create a Food token for each creature you control. (It's an artifact with "{2}, {T}, Sacrifice this token: You gain 3 life.")</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="270" customHeight="1">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>The Walls of Ba Sing Se</t>
-        </is>
-      </c>
-      <c r="C86" t="b">
-        <v>1</v>
-      </c>
-      <c r="D86" t="b">
-        <v>0</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>On Theme</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Mythic</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>TLA</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J86">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=The%20Walls%20of%20Ba%20Sing%20Se&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>$24.11</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Defender Other permanents you control have indestructible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="270" customHeight="1">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Thought Vessel</t>
-        </is>
-      </c>
-      <c r="C87" t="b">
-        <v>1</v>
-      </c>
-      <c r="D87" t="b">
-        <v>0</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>FIC</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J87">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Thought%20Vessel&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>$2.33</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>You have no maximum hand size. {T}: Add {C}.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="270" customHeight="1">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Threefold Thunderhulk</t>
-        </is>
-      </c>
-      <c r="C88" t="b">
-        <v>1</v>
-      </c>
-      <c r="D88" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>7 CMC for a 3/3 that makes 3 gnome tokens on entry — doesn't meet the dramatic impact bar at that cost; replaced by Cathars' Crusade for permanent board growth.</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>On Theme</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>EOC</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J88">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Threefold%20Thunderhulk&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>$0.31</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>This creature enters with three +1/+1 counters on it. Whenever this creature enters or attacks, create a number of 1/1 colorless Gnome artifact creature tokens equal to its power. {2}, Sacrifice another artifact: Put a +1/+1 counter on this creature.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="270" customHeight="1">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Thriving Heath</t>
-        </is>
-      </c>
-      <c r="C89" t="b">
-        <v>1</v>
-      </c>
-      <c r="D89" t="b">
-        <v>0</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Lands</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>ECC</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J89">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Thriving%20Heath&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>$0.23</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>This land enters tapped. As it enters, choose a color other than white. {T}: Add {W} or one mana of the chosen color.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="270" customHeight="1">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Thriving Isle</t>
-        </is>
-      </c>
-      <c r="C90" t="b">
-        <v>1</v>
-      </c>
-      <c r="D90" t="b">
-        <v>0</v>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Lands</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>TMC</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J90">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Thriving%20Isle&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>$0.27</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>This land enters tapped. As it enters, choose a color other than blue. {T}: Add {U} or one mana of the chosen color.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="270" customHeight="1">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Tocasia's Welcome</t>
-        </is>
-      </c>
-      <c r="C91" t="b">
-        <v>1</v>
-      </c>
-      <c r="D91" t="b">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Card Advantage</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>SOC</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J91">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Tocasia%27s%20Welcome&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>$0.66</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Whenever one or more creatures you control with mana value 3 or less enter, draw a card. This ability triggers only once each turn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="270" customHeight="1">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Uneasy Alliance</t>
-        </is>
-      </c>
-      <c r="C92" t="b">
-        <v>1</v>
-      </c>
-      <c r="D92" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Weakest interaction piece — pacifism with an awkward {5} exile upgrade; replaced by Ghostly Prison to tax all attackers.</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>On Theme</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>TMT</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J92">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Uneasy%20Alliance&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>$0.11</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Enchant creature Enchanted creature can't attack or block. {5}, Sacrifice this Aura: Exile enchanted creature. You create a 1/1 black Ninja creature token. Activate only as a sorcery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="270" customHeight="1">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Wayfarer's Bauble</t>
-        </is>
-      </c>
-      <c r="C93" t="b">
-        <v>1</v>
-      </c>
-      <c r="D93" t="b">
-        <v>0</v>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>FIC</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Wayfarer%27s%20Bauble&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>$0.24</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>{2}, {T}, Sacrifice this artifact: Search your library for a basic land card, put that card onto the battlefield tapped, then shuffle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="270" customHeight="1">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Welcoming Vampire</t>
-        </is>
-      </c>
-      <c r="C94" t="b">
-        <v>1</v>
-      </c>
-      <c r="D94" t="b">
-        <v>0</v>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Card Advantage</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>TDC</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J94">
-        <f>IMAGE("https://api.scryfall.com/cards/named?exact=Welcoming%20Vampire&amp;format=image&amp;version=normal")</f>
-        <v/>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>$2.98</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Flying Whenever one or more other creatures you control with power 2 or less enter, draw a card. This ability triggers only once each turn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
           <t>Total Cost (Have Physical Copy = false)</t>
         </is>
       </c>
-      <c r="K96" s="2">
-        <f>SUMPRODUCT(--(LOWER(TEXT($C$2:$C$94,"@"))="false"),IFERROR(VALUE(SUBSTITUTE($K$2:$K$94,"$","")),0))</f>
+      <c r="K79" s="2">
+        <f>SUMPRODUCT(--(LOWER(TEXT($C$2:$C$77,"@"))="false"),IFERROR(VALUE(SUBSTITUTE($K$2:$K$77,"$","")),0))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C94">
+  <conditionalFormatting sqref="C2:C77">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>=OR($C2=TRUE,LOWER(TEXT($C2,"@"))="true")</formula>
     </cfRule>
@@ -5548,7 +4575,7 @@
       <formula>=OR($C2=FALSE,LOWER(TEXT($C2,"@"))="false")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D94">
+  <conditionalFormatting sqref="D2:D77">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>=OR($D2=TRUE,LOWER(TEXT($D2,"@"))="true")</formula>
     </cfRule>
